--- a/docs/Berechtigungsmatrix.xlsx
+++ b/docs/Berechtigungsmatrix.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,12 +64,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="008a5a00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
@@ -86,12 +80,8 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="008a5a00"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="008A97A5"/>
+      <b val="1"/>
+      <color rgb="001C2230"/>
       <sz val="10"/>
     </font>
     <font>
@@ -101,12 +91,17 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="008A97A5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001D1F4E"/>
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -135,11 +130,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE9CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="001D1F4E"/>
       </patternFill>
     </fill>
@@ -149,7 +139,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -171,11 +161,55 @@
         <color rgb="00D9DEE6"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9DEE6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9DEE6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9DEE6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9DEE6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9DEE6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9DEE6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9DEE6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9DEE6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -199,49 +233,51 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -608,14 +644,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -628,7 +665,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rollen × Features (Lastenheft) · Coachingspace GmbH</t>
+          <t>Stand Workshop 11.06.2026 · Vorschlag zum Bestätigen/Anpassen durch die ZSB · Coachingspace GmbH</t>
         </is>
       </c>
     </row>
@@ -645,12 +682,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Nutzen</t>
+          <t>Beitragen</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Lesen</t>
+          <t>Ansehen</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -658,81 +695,67 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Geltungsbereich in Klammern: alle / betreute Schulen / Schule / eigene</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Doppelrollen möglich (z. B. Admin + Trainer:in) – Rechte addieren sich.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Admin (ZSB)</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Trainer:in (ZSB)</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Koordination (Schule)</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>Schüler:in (perspekt.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>1 · Lernen &amp; Inhalte</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr"/>
-      <c r="C6" s="12" t="inlineStr"/>
-      <c r="D6" s="12" t="inlineStr"/>
-      <c r="E6" s="12" t="inlineStr"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Trainer:in</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Koordination (Lehrkraft)</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Schüler:in (Coach)</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Hinweis</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Materialien ansehen / nutzen (Suche, Tags)</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Verwalten</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
-        </is>
-      </c>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>1 · Material &amp; Inhalte</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Inhalte/Materialien pflegen (CMS)</t>
+          <t>Material ansehen / suchen</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -742,24 +765,31 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Lesen</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Ansehen
+(betreute)</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen
+(Teilmenge)</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Suche über Kategorien/Tags (keine PDF-Volltextsuche)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Zeitgesteuerte Freischaltung steuern</t>
+          <t>Material hochladen &amp; taggen</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -767,26 +797,31 @@
           <t>Verwalten</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Nur Admin – kuratierte Qualität</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Schuljahres-Phasen/Struktur pflegen</t>
+          <t>Sichtbarkeit/Freigabe festlegen</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -794,53 +829,63 @@
           <t>Verwalten</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Lesen</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>„alle“ oder „nur Lehrkräfte“</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>FAQ nutzen (Selbsthilfe)</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
+          <t>Zeitgesteuerte Freischaltung</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Verwalten</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>z. B. Übergangsmaterial erst im letzten Quartal</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>FAQ pflegen</t>
+          <t>Kategorien &amp; Tags pflegen</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -848,64 +893,75 @@
           <t>Verwalten</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>feste Kategorien, zentral</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Onboarding durchlaufen</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
-        </is>
-      </c>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2 · Termine</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>2 · Kommunikation / Chat</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr"/>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="12" t="inlineStr"/>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Globale Termine (Abschlussfeier, Fortbildung)</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Verwalten</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Admin → alle; Empfänger nur zu-/absagen</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Schulgruppen-Chat</t>
+          <t>Trainingstermine</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -913,26 +969,32 @@
           <t>Verwalten</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen
+(betreute)</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
+          <t>Ansehen</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>Trainer:in für betreute Schulen (~3/Jahr)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Partnerschulgruppen-Chat</t>
+          <t>Tandem-Termine</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -940,80 +1002,93 @@
           <t>Verwalten</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen
+(eigene Schule)</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Koordination; Partnerschule sieht automatisch</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Frei definierbare Gruppen</t>
+          <t>Termine ansehen</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Verwalten</t>
+          <t>Verwalten
+(alle)</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>Lesen</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Ansehen
+(betreute)</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen
+(Schule)</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen
+(eigene)</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Direktnachrichten</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>Verwalten</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
-        </is>
-      </c>
+          <t>Teilnahme zu-/absagen</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen
+(eigene)</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Wichtige Nachricht „Sticky“</t>
+          <t>Warnung fehlende Termine</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -1023,377 +1098,444 @@
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Ansehen
+(betreute)</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Admin-Dashboard / Ampel gelb</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>3 · Organisation – Termine &amp; Kalender</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr"/>
-      <c r="C20" s="12" t="inlineStr"/>
-      <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr"/>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>3 · Kommunikation (Jugendschutz)</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Termine ansehen</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
+          <t>Event-Nachrichten erhalten</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>Termin abgesagt/verschoben/neu – an eigene Termine gekoppelt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Direktnachricht Koord ↔ Trainer</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Verwalten</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>beide Richtungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Direktnachricht Koord ↔ Koord</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Verwalten</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>nur Koordinationen einer Tandem-Schule</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Direktnachricht Trainer ↔ Admin</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Schüler-Chat</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>BEWUSST NICHT vorgesehen (Jugendschutz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Gruppenchat Tandem-Teams</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Verwalten</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>OFFEN – wg. Jugendschutz zu klären</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>4 · Feedback &amp; Monitoring</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Termin-Feedback (Smiley)</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>nach Training/Tandem-Treffen; bei „schlecht“ Textfeld</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Reflexion schreiben</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>Koordination, optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Ampel-Umfrage (alle 6 Wochen)</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>„Wie läuft das Projekt?“ grün/gelb/rot</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>„Hilfe nötig?“ / SOS auslösen</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>Schüler (nicht-akut) + Koordination → ZSB</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>Monitoring/Ampel-Übersicht</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>Verwalten
 (alle)</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen
 (betreute)</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen
 (Schule)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.
-(eigene)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Termine anlegen/verwalten</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>Verwalten</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen
-(global/Training)</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen
-(Schule)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.
-(vorschlagen)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>Kalender (persönlich/schul/global)</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>Verwalten</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Terminabstimmung</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Verwalten</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>Erinnerungen erhalten (Push/E-Mail)</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>4 · Feedback &amp; Monitoring</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr"/>
-      <c r="C26" s="12" t="inlineStr"/>
-      <c r="D26" s="12" t="inlineStr"/>
-      <c r="E26" s="12" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Feedback geben („Wie lief es?“)</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>Bedarfsmeldung („Hilfe nötig?“)</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>Auswertung/Diagramme sehen</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Auswertung / Diagramme</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>Verwalten
 (alle)</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen
 (betreute)</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen
 (Schule)</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>5 · Formulare</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr"/>
-      <c r="C30" s="12" t="inlineStr"/>
-      <c r="D30" s="12" t="inlineStr"/>
-      <c r="E30" s="12" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>Formulare ausfüllen</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>Formulare zuweisen / Status verwalten</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>Verwalten</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen
-(betreute)</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen
-(Schule)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>6 · Benutzer- &amp; Rollenverwaltung</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr"/>
-      <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="12" t="inlineStr"/>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>Schulen anlegen</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>Verwalten</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>5 · Export &amp; Zertifikate</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>Nutzer einladen/zuweisen</t>
+          <t>Daten-/Excel-Export</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -1401,28 +1543,31 @@
           <t>Verwalten</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen
-(betreute)</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>Nutzen
-(eigene Schule)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>Statistiken, Stadtverteilung, Stimmung, Namen</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>Trainer zuweisen</t>
+          <t>Zertifikat erstellen/abrufen</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
@@ -1430,53 +1575,41 @@
           <t>Verwalten</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="D36" s="18" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Beitragen
+(eigene SuS)</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Ansehen
+(eigenes)</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
-        <is>
-          <t>Jahreswechsel-Logik</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Verwalten</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>6 · Nutzer-, Schul- &amp; Jahresverwaltung</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>Rollen-/Rechteverwaltung</t>
+          <t>Schulen anlegen/bearbeiten</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
@@ -1484,48 +1617,225 @@
           <t>Verwalten</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>Schul-Kooperation zuordnen (1:n)</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Verwalten</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>1 weiterführende ↔ bis 3 Grundschulen</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>Geltungsbereich: Admin = systemweit · Trainer = betreute Schulen · Koordination = eigene Schule (serverseitig per RLS).</t>
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>Koordinator:innen/Trainer:innen anlegen</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Verwalten</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>+ Login-Daten</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>Schüler:in = laut Lastenheft „perspektivisch“ (im Prototyp bereits als Coach umgesetzt). Koordination ≈ Lehrkraft. Trainer-Rolle im Prototyp noch nicht abgebildet (Admin deckt ZSB ab).</t>
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>Trainer ↔ Schule zuweisen/auflösen</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Verwalten</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>Trainer:in kann nicht selbst lösen</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>Schüler-Chat: startet keine Erwachsenen-Gespräche, darf aber antworten; Lehrkraft↔Schüler-Chats für die Koordination einsehbar (Kinderschutz).</t>
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>Schüler-Registrierung freigeben/sperren</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Verwalten</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen
+(eigene Schule)</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>QR-Anmeldung, Koordination bestätigt einzeln</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>Schüler entfernen/korrigieren</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Verwalten</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>Beitragen
+(eigene)</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>mit Verlauf/Historie (kein Überschreiben)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>Schuljahr / Jahreswechsel verwalten</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Verwalten</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>Enddatum, Auto-Löschung SuS am Jahresende</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A41:E41"/>
+  <mergeCells count="6">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1537,162 +1847,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>Direktchat – wer darf wen anschreiben?</t>
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Direktchat / Kommunikation – wer darf wen anschreiben?</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ja = darf initiieren · — = nein · eingeschränkt = nur antworten / perspektivisch</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>Initiator ↓ \ Empfänger →</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
+          <t>ja = erlaubt · — = nicht vorgesehen · Schüler:innen: KEIN Chat (nur Event-Nachrichten + SOS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Initiator \ Empfänger</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Koordination</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Schüler:in</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Trainer</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Koordination</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Koordination</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>ja</t>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>ja*</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Schüler:in</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>nur antworten</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>perspekt.</t>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>*  Koordination ↔ Koordination nur zwischen den Koordinationen einer Tandem-Schule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>Statt freiem Chat: event-basierte Vorlage-Nachrichten (Termin abgesagt/verschoben/neu).</t>
         </is>
       </c>
     </row>
